--- a/.ai_keep/workshops/toonflow-field-survival/map_design/通天传授-收徒系统/data.xlsx
+++ b/.ai_keep/workshops/toonflow-field-survival/map_design/通天传授-收徒系统/data.xlsx
@@ -7620,7 +7620,7 @@
         <v>97</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8219,381 +8219,381 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FOUNTAIN</t>
+          <t>FLAIL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fountain</t>
+          <t>flail</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>喷泉</t>
+          <t>连枷</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6449,6457</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GRASS</t>
+          <t>FOUNTAIN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>grass</t>
+          <t>fountain</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>草地</t>
+          <t>喷泉</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7387,7389,7627,7628,7629,7747,7749,7987,7988,7989,8107,8109,8347,8348,8349,8463,8465,8467,8469</t>
+          <t>6449,6457</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>GRASS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>unregistered</t>
+          <t>grass</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>未登记杂项</t>
+          <t>草地</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>147</v>
+        <v>5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>23,33,37,55,59,151,175,477,479,487,567,607,687,689,691,695,783,809,831,969,1241,1255,1361,1479,1601,1727,1729,2279,2317,2551,2557,2643,3095,3215,3335,3455,3575,3695,3855,3927,3967,3973,4047,4175,4287,4407,4695,4767,4887,5007,5127,5171,5247,5291,5295,5297,5367,5533,5535,5537,5607,5727,5847,6087,6447,6463,7025,7045,7351,7365,7419,7439,7441,7443,7445,7471,7485,7487,7591,7659,7711,7727,7735,7755,7763,7779,7833,7835,7837,7855,7883,7935,7953,7975,8003,8123,8175,8243,8295,8455,8471,8501,8575,8583,8585,8587,8589,8591,8695,8711,8983,9203,9205,9223,9323,9327,9341,9443,9445,9895,10015,10063,10135,10383,10615,10617,10629,10735,10737,10743,10745,10749,10855,10857,10863,10865,10869,10987,11105,11107,11109,11223,11225,11341,11349,11469,11589</t>
+          <t>7387,7389,7627,7628,7629,7747,7749,7987,7988,7989,8107,8109,8347,8348,8349,8463,8465,8467,8469</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MUSHROOM</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mushroom</t>
+          <t>unregistered</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>蘑菇</t>
+          <t>未登记杂项</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1605,1724,1725</t>
+          <t>23,33,37,55,59,151,175,477,479,487,567,607,687,689,691,695,783,809,831,969,1241,1255,1361,1479,1601,1727,1729,2279,2317,2551,2557,2643,3095,3215,3335,3455,3575,3695,3855,3927,3967,3973,4047,4175,4287,4407,4695,4767,4887,5007,5127,5171,5247,5291,5295,5297,5367,5533,5535,5537,5607,5727,5847,6087,6447,6463,7025,7045,7351,7365,7419,7439,7441,7443,7445,7471,7485,7487,7591,7659,7711,7727,7735,7755,7763,7779,7833,7835,7837,7855,7883,7935,7953,7975,8003,8123,8175,8243,8295,8455,8471,8501,8575,8583,8585,8587,8589,8591,8695,8711,8983,9203,9205,9223,9323,9327,9341,9443,9445,9895,10015,10063,10135,10383,10615,10617,10629,10735,10737,10743,10745,10749,10855,10857,10863,10865,10869,10987,11105,11107,11109,11223,11225,11341,11349,11469,11589</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WILD_GRASS</t>
+          <t>MUSHROOM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wild grass</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>野草</t>
+          <t>蘑菇</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1242,1243,1244,1245,1250,1251,1252,1253,1362,1363,1364,1365,1370,1371,1372,1373</t>
+          <t>1605,1724,1725</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WOODEN_FLOOR</t>
+          <t>SHRUB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wooden floor</t>
+          <t>shrub</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>木地板</t>
+          <t>灌木</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8703,8705,8709,8827,8829,9067,9068,9069,9187,9189,9427,9428,9429,9547,9549,9787,9788,9789,9907,9909,10147,10148,10149</t>
+          <t>1722,1723,1726</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WOODEN_WALL</t>
+          <t>WILD_GRASS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wooden wall</t>
+          <t>wild grass</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>木墙</t>
+          <t>野草</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>16</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7409,7645,7647,7649,7769,8005,8007,8009,8129,8365,8367,8369,8489,8725,8727,8729</t>
+          <t>1242,1243,1244,1245,1250,1251,1252,1253,1362,1363,1364,1365,1370,1371,1372,1373</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COBBLE_STONE_FLOOR</t>
+          <t>WOODEN_FLOOR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>cobble stone floor</t>
+          <t>wooden floor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>鹅卵石地板</t>
+          <t>木地板</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10274,10276,10514,10515,10516</t>
+          <t>8703,8705,8709,8827,8829,9067,9068,9069,9187,9189,9427,9428,9429,9547,9549,9787,9788,9789,9907,9909,10147,10148,10149</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>WOODEN_WALL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>dirt</t>
+          <t>wooden wall</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>泥土</t>
+          <t>木墙</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>8820,8822,9060,9061,9062,9180,9182,9420,9421,9422,9540,9542,9780,9781,9782,9900,9902,10140,10141,10142</t>
+          <t>7409,7645,7647,7649,7769,8005,8007,8009,8129,8365,8367,8369,8489,8725,8727,8729</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DIRT_WALL</t>
+          <t>COBBLE_STONE_FLOOR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dirt wall</t>
+          <t>cobble stone floor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>土墙</t>
+          <t>鹅卵石地板</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>8842,9078,9080,9082,9202,9438,9440,9442,9562,9798,9800,9802,9922,10158,10160,10162</t>
+          <t>10274,10276,10514,10515,10516</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FLAIL</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>flail</t>
+          <t>dirt</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>连枷</t>
+          <t>泥土</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>8820,8822,9060,9061,9062,9180,9182,9420,9421,9422,9540,9542,9780,9781,9782,9900,9902,10140,10141,10142</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LOGS</t>
+          <t>DIRT_WALL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>logs</t>
+          <t>dirt wall</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>原木</t>
+          <t>土墙</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5254,5262</t>
+          <t>8842,9078,9080,9082,9202,9438,9440,9442,9562,9798,9800,9802,9922,10158,10160,10162</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MINE_WALL</t>
+          <t>LOGS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>mine wall</t>
+          <t>logs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>矿墙</t>
+          <t>原木</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>7416,7652,7654,7656,7776,8012,8014,8016,8136,8372,8374,8376,8496,8732,8734,8736</t>
+          <t>5254,5262</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MOSSY_STONE_WALL</t>
+          <t>MINE_WALL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mossy stone wall</t>
+          <t>mine wall</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>苔石墙</t>
+          <t>矿墙</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -8604,52 +8604,52 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10302,10538,10540,10542,10662,10898,10900,10902,11022,11258,11260,11262,11382,11618,11620,11622</t>
+          <t>7416,7652,7654,7656,7776,8012,8014,8016,8136,8372,8374,8376,8496,8732,8734,8736</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PEDESTAL</t>
+          <t>MOSSY_STONE_WALL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>mossy stone wall</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>基座</t>
+          <t>苔石墙</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>5734,6328,6336</t>
+          <t>10302,10538,10540,10542,10662,10898,10900,10902,11022,11258,11260,11262,11382,11618,11620,11622</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SHRUB</t>
+          <t>PEDESTAL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>shrub</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>灌木</t>
+          <t>基座</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1722,1723,1726</t>
+          <t>5734,6328,6336</t>
         </is>
       </c>
     </row>
